--- a/Data/2025_upperhouse_election_constituency_system.xlsx
+++ b/Data/2025_upperhouse_election_constituency_system.xlsx
@@ -3391,7 +3391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
       <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21.75">
       <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="21.75">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21.75">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21.75">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21.75">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="21.75">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="21.75">
       <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21.75">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="21.75">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="21.75">
       <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="21.75">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
